--- a/docs/d/206/inyear.xlsx
+++ b/docs/d/206/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 64 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 59 clubs short</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3137,8 +3137,8 @@
       <c r="Y25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z25" s="9" t="n">
-        <v>0</v>
+      <c r="Z25" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA25" s="10" t="n">
         <v>1</v>
@@ -5436,7 +5436,7 @@
         </is>
       </c>
       <c r="P49" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q49" s="9" t="n">
         <v>0</v>
@@ -6526,8 +6526,8 @@
       <c r="W60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X60" s="9" t="n">
-        <v>3</v>
+      <c r="X60" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y60" s="9" t="n">
         <v>0</v>
@@ -8370,7 +8370,7 @@
         <v>0</v>
       </c>
       <c r="X79" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y79" s="9" t="n">
         <v>0</v>
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>0</v>
       </c>
       <c r="V81" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W81" s="9" t="n">
         <v>0</v>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -9871,13 +9871,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
@@ -9915,8 +9915,8 @@
       <c r="U95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V95" s="9" t="n">
-        <v>3</v>
+      <c r="V95" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
@@ -9954,7 +9954,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10024,8 +10024,8 @@
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="9" t="n">
-        <v>0</v>
+      <c r="Z96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA96" s="10" t="n">
         <v>1</v>
@@ -10536,7 +10536,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -10606,8 +10606,8 @@
       <c r="Y102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z102" s="9" t="n">
-        <v>0</v>
+      <c r="Z102" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA102" s="10" t="n">
         <v>1</v>
@@ -13058,7 +13058,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13128,8 +13128,8 @@
       <c r="Y128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z128" s="9" t="n">
-        <v>0</v>
+      <c r="Z128" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA128" s="10" t="n">
         <v>1</v>
@@ -14319,7 +14319,7 @@
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -14360,7 +14360,7 @@
         </is>
       </c>
       <c r="P141" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q141" s="9" t="n">
         <v>0</v>
@@ -14389,8 +14389,8 @@
       <c r="Y141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z141" s="9" t="n">
-        <v>0</v>
+      <c r="Z141" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA141" s="10" t="n">
         <v>1</v>
@@ -16847,7 +16847,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -17342,7 +17342,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -17375,7 +17375,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -17540,7 +17540,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>

--- a/docs/d/206/inyear.xlsx
+++ b/docs/d/206/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/206/inyear.xlsx
+++ b/docs/d/206/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 10 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 10 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 59 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 53 clubs short</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2143,8 +2143,8 @@
       <c r="Q15" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R15" s="9" t="n">
-        <v>0</v>
+      <c r="R15" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S15" s="9" t="n">
         <v>0</v>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2431,14 +2431,14 @@
       <c r="P18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" s="9" t="n">
-        <v>0</v>
+      <c r="Q18" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" s="9" t="n">
         <v>0</v>
@@ -3020,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="S24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24" s="9" t="n">
         <v>0</v>
@@ -6527,7 +6527,7 @@
         <v>0</v>
       </c>
       <c r="X60" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y60" s="9" t="n">
         <v>0</v>
@@ -7206,7 +7206,7 @@
         <v>0</v>
       </c>
       <c r="X67" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y67" s="9" t="n">
         <v>0</v>
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7405,8 +7405,8 @@
       <c r="Y69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z69" s="9" t="n">
-        <v>0</v>
+      <c r="Z69" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA69" s="10" t="n">
         <v>1</v>
@@ -7690,8 +7690,8 @@
       <c r="W72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X72" s="9" t="n">
-        <v>3</v>
+      <c r="X72" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y72" s="9" t="n">
         <v>0</v>
@@ -8637,7 +8637,7 @@
         </is>
       </c>
       <c r="P82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q82" s="9" t="n">
         <v>0</v>
@@ -10310,7 +10310,7 @@
         <v>0</v>
       </c>
       <c r="X99" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y99" s="9" t="n">
         <v>0</v>
@@ -11280,7 +11280,7 @@
         <v>0</v>
       </c>
       <c r="X109" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y109" s="9" t="n">
         <v>0</v>
@@ -12670,7 +12670,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -12740,8 +12740,8 @@
       <c r="Y124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z124" s="9" t="n">
-        <v>0</v>
+      <c r="Z124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA124" s="10" t="n">
         <v>1</v>
@@ -13446,7 +13446,7 @@
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -13516,8 +13516,8 @@
       <c r="Y132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z132" s="9" t="n">
-        <v>0</v>
+      <c r="Z132" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA132" s="10" t="n">
         <v>1</v>
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -14486,8 +14486,8 @@
       <c r="Y142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z142" s="9" t="n">
-        <v>0</v>
+      <c r="Z142" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA142" s="10" t="n">
         <v>1</v>
@@ -15095,7 +15095,7 @@
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F149" s="6" t="n">
         <v>10</v>
@@ -15165,8 +15165,8 @@
       <c r="Y149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z149" s="9" t="n">
-        <v>0</v>
+      <c r="Z149" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA149" s="10" t="n">
         <v>1</v>
@@ -16550,7 +16550,7 @@
         </is>
       </c>
       <c r="E164" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F164" s="6" t="n">
         <v>10</v>
@@ -16620,8 +16620,8 @@
       <c r="Y164" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z164" s="9" t="n">
-        <v>0</v>
+      <c r="Z164" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA164" s="10" t="n">
         <v>1</v>
@@ -16781,7 +16781,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -16814,7 +16814,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -17144,7 +17144,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -17507,7 +17507,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -17573,7 +17573,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -17705,7 +17705,7 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -17771,7 +17771,7 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>

--- a/docs/d/206/inyear.xlsx
+++ b/docs/d/206/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 10 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 10 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 53 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 27 clubs short</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -906,8 +906,8 @@
       <c r="Y2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="9" t="n">
-        <v>0</v>
+      <c r="Z2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA2" s="10" t="n">
         <v>1</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1488,8 +1488,8 @@
       <c r="Y8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="9" t="n">
-        <v>0</v>
+      <c r="Z8" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA8" s="10" t="n">
         <v>1</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1579,14 +1579,14 @@
       <c r="W9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X9" s="9" t="n">
-        <v>3</v>
+      <c r="X9" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" s="9" t="n">
-        <v>0</v>
+      <c r="Z9" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA9" s="10" t="n">
         <v>1</v>
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1876,8 +1876,8 @@
       <c r="Y12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" s="9" t="n">
-        <v>0</v>
+      <c r="Z12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA12" s="10" t="n">
         <v>1</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -1973,8 +1973,8 @@
       <c r="Y13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z13" s="9" t="n">
-        <v>0</v>
+      <c r="Z13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA13" s="10" t="n">
         <v>1</v>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2014,13 +2014,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W14" s="9" t="n">
         <v>0</v>
@@ -2070,8 +2070,8 @@
       <c r="Y14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" s="9" t="n">
-        <v>0</v>
+      <c r="Z14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA14" s="10" t="n">
         <v>1</v>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2458,8 +2458,8 @@
       <c r="Y18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z18" s="9" t="n">
-        <v>0</v>
+      <c r="Z18" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA18" s="10" t="n">
         <v>1</v>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
@@ -2652,8 +2652,8 @@
       <c r="Y20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z20" s="9" t="n">
-        <v>0</v>
+      <c r="Z20" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA20" s="10" t="n">
         <v>1</v>
@@ -3040,8 +3040,8 @@
       <c r="Y24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z24" s="9" t="n">
-        <v>0</v>
+      <c r="Z24" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA24" s="9" t="n">
         <v>0</v>
@@ -3358,7 +3358,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3428,8 +3428,8 @@
       <c r="Y28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z28" s="9" t="n">
-        <v>0</v>
+      <c r="Z28" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA28" s="10" t="n">
         <v>1</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3525,8 +3525,8 @@
       <c r="Y29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z29" s="9" t="n">
-        <v>0</v>
+      <c r="Z29" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA29" s="10" t="n">
         <v>1</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4107,8 +4107,8 @@
       <c r="Y35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z35" s="9" t="n">
-        <v>0</v>
+      <c r="Z35" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA35" s="10" t="n">
         <v>1</v>
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4301,8 +4301,8 @@
       <c r="Y37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z37" s="9" t="n">
-        <v>0</v>
+      <c r="Z37" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA37" s="10" t="n">
         <v>1</v>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4592,8 +4592,8 @@
       <c r="Y40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z40" s="9" t="n">
-        <v>0</v>
+      <c r="Z40" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA40" s="10" t="n">
         <v>1</v>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4786,8 +4786,8 @@
       <c r="Y42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z42" s="9" t="n">
-        <v>0</v>
+      <c r="Z42" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA42" s="10" t="n">
         <v>1</v>
@@ -5312,13 +5312,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>1</v>
       </c>
       <c r="V48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>0</v>
@@ -6139,7 +6139,7 @@
         <v>0</v>
       </c>
       <c r="X56" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y56" s="9" t="n">
         <v>0</v>
@@ -6333,7 +6333,7 @@
         <v>0</v>
       </c>
       <c r="X58" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y58" s="9" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6629,8 +6629,8 @@
       <c r="Y61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z61" s="9" t="n">
-        <v>0</v>
+      <c r="Z61" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA61" s="10" t="n">
         <v>1</v>
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -6721,13 +6721,13 @@
         <v>0</v>
       </c>
       <c r="X62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z62" s="9" t="n">
-        <v>0</v>
+      <c r="Z62" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA62" s="10" t="n">
         <v>1</v>
@@ -7109,7 +7109,7 @@
         <v>0</v>
       </c>
       <c r="X66" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y66" s="9" t="n">
         <v>0</v>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8278,8 +8278,8 @@
       <c r="Y78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z78" s="9" t="n">
-        <v>0</v>
+      <c r="Z78" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA78" s="10" t="n">
         <v>1</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -8763,8 +8763,8 @@
       <c r="Y83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z83" s="9" t="n">
-        <v>0</v>
+      <c r="Z83" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA83" s="10" t="n">
         <v>1</v>
@@ -8887,7 +8887,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -8930,8 +8930,8 @@
       <c r="P85" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q85" s="9" t="n">
-        <v>1</v>
+      <c r="Q85" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R85" s="9" t="n">
         <v>0</v>
@@ -8939,8 +8939,8 @@
       <c r="S85" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T85" s="9" t="n">
-        <v>0</v>
+      <c r="T85" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U85" s="9" t="n">
         <v>0</v>
@@ -9319,7 +9319,7 @@
         <v>0</v>
       </c>
       <c r="Q89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R89" s="9" t="n">
         <v>0</v>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q105" s="9" t="n">
         <v>0</v>
@@ -11021,7 +11021,7 @@
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11091,8 +11091,8 @@
       <c r="Y107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z107" s="9" t="n">
-        <v>0</v>
+      <c r="Z107" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA107" s="10" t="n">
         <v>1</v>
@@ -11547,7 +11547,7 @@
         </is>
       </c>
       <c r="P112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q112" s="9" t="n">
         <v>0</v>
@@ -11938,7 +11938,7 @@
         <v>1</v>
       </c>
       <c r="Q116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R116" s="9" t="n">
         <v>0</v>
@@ -12235,7 +12235,7 @@
         <v>0</v>
       </c>
       <c r="S119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T119" s="9" t="n">
         <v>0</v>
@@ -12379,7 +12379,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -12449,8 +12449,8 @@
       <c r="Y121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z121" s="9" t="n">
-        <v>0</v>
+      <c r="Z121" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA121" s="10" t="n">
         <v>1</v>
@@ -12517,7 +12517,7 @@
         </is>
       </c>
       <c r="P122" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q122" s="9" t="n">
         <v>0</v>
@@ -13807,8 +13807,8 @@
       <c r="Y135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z135" s="9" t="n">
-        <v>0</v>
+      <c r="Z135" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA135" s="9" t="n">
         <v>0</v>
@@ -13931,7 +13931,7 @@
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -14001,8 +14001,8 @@
       <c r="Y137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z137" s="9" t="n">
-        <v>0</v>
+      <c r="Z137" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA137" s="10" t="n">
         <v>1</v>
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -14777,8 +14777,8 @@
       <c r="Y145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z145" s="9" t="n">
-        <v>0</v>
+      <c r="Z145" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA145" s="10" t="n">
         <v>1</v>
@@ -15871,7 +15871,7 @@
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>10</v>
@@ -15941,8 +15941,8 @@
       <c r="Y157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z157" s="9" t="n">
-        <v>0</v>
+      <c r="Z157" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA157" s="10" t="n">
         <v>1</v>
@@ -16106,7 +16106,7 @@
         </is>
       </c>
       <c r="P159" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q159" s="9" t="n">
         <v>0</v>
@@ -16162,7 +16162,7 @@
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -16232,8 +16232,8 @@
       <c r="Y160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z160" s="9" t="n">
-        <v>0</v>
+      <c r="Z160" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA160" s="10" t="n">
         <v>1</v>
@@ -16715,7 +16715,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -16748,7 +16748,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -16781,7 +16781,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -16814,7 +16814,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -16880,7 +16880,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -16913,7 +16913,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -16946,7 +16946,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -16979,7 +16979,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -17111,7 +17111,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -17210,7 +17210,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -17243,7 +17243,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -17276,7 +17276,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -17408,7 +17408,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -17507,7 +17507,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -17606,7 +17606,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -17672,7 +17672,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -17738,7 +17738,7 @@
         <v>6</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -17771,7 +17771,7 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>

--- a/docs/d/206/inyear.xlsx
+++ b/docs/d/206/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 10 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 10 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 27 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 27 clubs short</t>
         </is>
       </c>
     </row>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1238,13 +1238,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" s="9" t="n">
         <v>0</v>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -2014,13 +2014,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="P20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" s="9" t="n">
         <v>0</v>
@@ -2693,17 +2693,17 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M21" s="8" t="n">
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
@@ -2790,13 +2790,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -3081,13 +3081,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3178,17 +3178,17 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M26" s="8" t="n">
@@ -3275,17 +3275,17 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M27" s="8" t="n">
@@ -3320,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -3469,17 +3469,17 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M29" s="8" t="n">
@@ -3566,13 +3566,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>4</v>
       </c>
       <c r="W30" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X30" s="10" t="n">
         <v>7</v>
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1</v>
+        <v>-16</v>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -3857,13 +3857,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
@@ -3901,11 +3901,11 @@
       <c r="U33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V33" s="9" t="n">
+      <c r="V33" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W33" s="9" t="n">
         <v>3</v>
-      </c>
-      <c r="W33" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="X33" s="10" t="n">
         <v>4</v>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
@@ -3990,10 +3990,10 @@
         <v>0</v>
       </c>
       <c r="S34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T34" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U34" s="9" t="n">
         <v>0</v>
@@ -4002,7 +4002,7 @@
         <v>4</v>
       </c>
       <c r="W34" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X34" s="10" t="n">
         <v>6</v>
@@ -4051,13 +4051,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
         <v>1</v>
       </c>
       <c r="V36" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>0</v>
@@ -4245,17 +4245,17 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M37" s="8" t="n">
@@ -4281,7 +4281,7 @@
         <v>0</v>
       </c>
       <c r="S37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T37" s="9" t="n">
         <v>0</v>
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>0</v>
@@ -4439,13 +4439,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>0</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" s="9" t="n">
         <v>0</v>
@@ -4574,8 +4574,8 @@
       <c r="S40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T40" s="9" t="n">
-        <v>0</v>
+      <c r="T40" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U40" s="9" t="n">
         <v>0</v>
@@ -4633,17 +4633,17 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M41" s="8" t="n">
@@ -4730,13 +4730,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -4924,13 +4924,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5065,8 +5065,8 @@
       <c r="U45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V45" s="9" t="n">
-        <v>3</v>
+      <c r="V45" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -5118,13 +5118,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5312,13 +5312,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
@@ -5603,13 +5603,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -5894,13 +5894,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -5991,13 +5991,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
@@ -6088,13 +6088,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6229,8 +6229,8 @@
       <c r="U57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V57" s="9" t="n">
-        <v>2</v>
+      <c r="V57" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W57" s="9" t="n">
         <v>0</v>
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="P58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q58" s="9" t="n">
         <v>0</v>
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>0</v>
       </c>
       <c r="V60" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W60" s="9" t="n">
         <v>0</v>
@@ -6573,17 +6573,17 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M61" s="8" t="n">
@@ -6812,7 +6812,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -6864,17 +6864,17 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L64" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M64" s="8" t="n">
@@ -7006,7 +7006,7 @@
         <v>0</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
@@ -7058,17 +7058,17 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L66" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M66" s="8" t="n">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7349,13 +7349,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
@@ -7490,8 +7490,8 @@
       <c r="U70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V70" s="9" t="n">
-        <v>2</v>
+      <c r="V70" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
@@ -7543,13 +7543,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -7640,13 +7640,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -7834,13 +7834,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>52</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>11</v>
+        <v>-9</v>
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>4</v>
       </c>
       <c r="W74" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X74" s="10" t="n">
         <v>5</v>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>0</v>
       </c>
       <c r="V76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8125,13 +8125,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>0</v>
       </c>
       <c r="V78" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
@@ -8319,17 +8319,17 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L79" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M79" s="8" t="n">
@@ -8364,7 +8364,7 @@
         <v>0</v>
       </c>
       <c r="V79" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
@@ -8416,13 +8416,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -8610,13 +8610,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -8707,17 +8707,17 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M83" s="8" t="n">
@@ -8752,7 +8752,7 @@
         <v>0</v>
       </c>
       <c r="V83" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
@@ -8804,17 +8804,17 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L84" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L84" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M84" s="8" t="n">
@@ -8834,7 +8834,7 @@
         <v>1</v>
       </c>
       <c r="Q84" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R84" s="9" t="n">
         <v>0</v>
@@ -8887,7 +8887,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -8901,17 +8901,17 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L85" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L85" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M85" s="8" t="n">
@@ -8936,8 +8936,8 @@
       <c r="R85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S85" s="9" t="n">
-        <v>1</v>
+      <c r="S85" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T85" s="10" t="n">
         <v>1</v>
@@ -8998,13 +8998,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9095,13 +9095,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9224,8 +9224,8 @@
       <c r="Q88" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R88" s="9" t="n">
-        <v>1</v>
+      <c r="R88" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S88" s="10" t="n">
         <v>2</v>
@@ -9289,13 +9289,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="P90" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q90" s="9" t="n">
         <v>0</v>
@@ -9483,13 +9483,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>0</v>
       </c>
       <c r="V91" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W91" s="9" t="n">
         <v>0</v>
@@ -9625,7 +9625,7 @@
         <v>0</v>
       </c>
       <c r="V92" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W92" s="9" t="n">
         <v>0</v>
@@ -9677,13 +9677,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -9774,13 +9774,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -9871,13 +9871,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>4</v>
       </c>
       <c r="W95" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X95" s="10" t="n">
         <v>4</v>
@@ -9968,13 +9968,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10065,13 +10065,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10162,13 +10162,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10197,8 +10197,8 @@
       <c r="R98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S98" s="9" t="n">
-        <v>1</v>
+      <c r="S98" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T98" s="9" t="n">
         <v>0</v>
@@ -10259,13 +10259,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>0</v>
       </c>
       <c r="V99" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>0</v>
       </c>
       <c r="V102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W102" s="9" t="n">
         <v>0</v>
@@ -10647,13 +10647,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -10744,13 +10744,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -10938,13 +10938,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11132,13 +11132,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>4</v>
       </c>
       <c r="W109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X109" s="10" t="n">
         <v>7</v>
@@ -11326,13 +11326,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -11423,13 +11423,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -11520,13 +11520,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
@@ -11617,13 +11617,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
@@ -11644,16 +11644,16 @@
         </is>
       </c>
       <c r="P113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T113" s="9" t="n">
         <v>0</v>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -12005,13 +12005,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
@@ -12102,17 +12102,17 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L118" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L118" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M118" s="8" t="n">
@@ -12185,7 +12185,7 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12199,13 +12199,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
@@ -12237,8 +12237,8 @@
       <c r="S119" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T119" s="9" t="n">
-        <v>0</v>
+      <c r="T119" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U119" s="9" t="n">
         <v>0</v>
@@ -12296,13 +12296,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>0</v>
       </c>
       <c r="V120" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W120" s="9" t="n">
         <v>0</v>
@@ -12393,13 +12393,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>0</v>
       </c>
       <c r="V122" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
@@ -12587,13 +12587,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -12632,7 +12632,7 @@
         <v>0</v>
       </c>
       <c r="V123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W123" s="9" t="n">
         <v>0</v>
@@ -12684,13 +12684,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>0</v>
       </c>
       <c r="V124" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W124" s="9" t="n">
         <v>0</v>
@@ -12781,17 +12781,17 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L125" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L125" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M125" s="8" t="n">
@@ -12826,7 +12826,7 @@
         <v>0</v>
       </c>
       <c r="V125" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W125" s="9" t="n">
         <v>0</v>
@@ -12878,13 +12878,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -13023,7 +13023,7 @@
         <v>4</v>
       </c>
       <c r="W127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X127" s="10" t="n">
         <v>4</v>
@@ -13072,13 +13072,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>0</v>
       </c>
       <c r="V128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
@@ -13169,17 +13169,17 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L129" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L129" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M129" s="8" t="n">
@@ -13266,13 +13266,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>0</v>
       </c>
       <c r="V130" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W130" s="9" t="n">
         <v>0</v>
@@ -13460,13 +13460,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -13557,13 +13557,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
@@ -13604,8 +13604,8 @@
       <c r="V133" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W133" s="9" t="n">
-        <v>3</v>
+      <c r="W133" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X133" s="10" t="n">
         <v>4</v>
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
@@ -13751,13 +13751,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>0</v>
       </c>
       <c r="V135" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W135" s="9" t="n">
         <v>0</v>
@@ -13848,13 +13848,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -13945,13 +13945,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -14042,13 +14042,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -14139,13 +14139,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
@@ -14183,11 +14183,11 @@
       <c r="U139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V139" s="9" t="n">
-        <v>3</v>
+      <c r="V139" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W139" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X139" s="9" t="n">
         <v>2</v>
@@ -14236,13 +14236,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -14333,13 +14333,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -14430,13 +14430,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -14527,13 +14527,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -14624,13 +14624,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
@@ -14665,8 +14665,8 @@
       <c r="T144" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U144" s="9" t="n">
-        <v>0</v>
+      <c r="U144" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V144" s="9" t="n">
         <v>3</v>
@@ -14721,13 +14721,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
@@ -14818,13 +14818,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L146" s="7" t="inlineStr">
         <is>
@@ -14915,17 +14915,17 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L147" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L147" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M147" s="8" t="n">
@@ -14960,7 +14960,7 @@
         <v>0</v>
       </c>
       <c r="V147" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W147" s="9" t="n">
         <v>0</v>
@@ -15012,13 +15012,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L148" s="7" t="inlineStr">
         <is>
@@ -15109,13 +15109,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
         <v>0</v>
       </c>
       <c r="V149" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W149" s="9" t="n">
         <v>0</v>
@@ -15206,17 +15206,17 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L150" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L150" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M150" s="8" t="n">
@@ -15251,7 +15251,7 @@
         <v>0</v>
       </c>
       <c r="V150" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W150" s="9" t="n">
         <v>0</v>
@@ -15303,13 +15303,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L151" s="4" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="V151" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W151" s="9" t="n">
         <v>0</v>
@@ -15400,13 +15400,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L152" s="7" t="inlineStr">
         <is>
@@ -15497,13 +15497,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
@@ -15594,17 +15594,17 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L154" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L154" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M154" s="8" t="n">
@@ -15639,7 +15639,7 @@
         <v>0</v>
       </c>
       <c r="V154" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W154" s="9" t="n">
         <v>0</v>
@@ -15691,17 +15691,17 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L155" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L155" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M155" s="8" t="n">
@@ -15736,7 +15736,7 @@
         <v>0</v>
       </c>
       <c r="V155" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W155" s="9" t="n">
         <v>0</v>
@@ -15774,7 +15774,7 @@
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -15788,13 +15788,13 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L156" s="7" t="inlineStr">
         <is>
@@ -15814,8 +15814,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P156" s="9" t="n">
-        <v>3</v>
+      <c r="P156" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q156" s="9" t="n">
         <v>1</v>
@@ -15885,17 +15885,17 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L157" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-24</v>
+      </c>
+      <c r="L157" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M157" s="8" t="n">
@@ -15982,17 +15982,17 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L158" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L158" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M158" s="8" t="n">
@@ -16079,13 +16079,13 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L159" s="7" t="inlineStr">
         <is>
@@ -16176,13 +16176,13 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L160" s="7" t="inlineStr">
         <is>
@@ -16273,13 +16273,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>0</v>
       </c>
       <c r="V161" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W161" s="9" t="n">
         <v>0</v>
@@ -16370,17 +16370,17 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L162" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L162" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M162" s="8" t="n">
@@ -16397,7 +16397,7 @@
         </is>
       </c>
       <c r="P162" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q162" s="10" t="n">
         <v>2</v>
@@ -16467,17 +16467,17 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L163" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L163" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M163" s="8" t="n">
@@ -16564,13 +16564,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L164" s="4" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -16862,7 +16862,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -16895,7 +16895,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -16913,7 +16913,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -16928,7 +16928,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -16946,7 +16946,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -16961,7 +16961,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -16979,7 +16979,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -17078,7 +17078,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -17126,7 +17126,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -17159,7 +17159,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -17177,7 +17177,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -17225,7 +17225,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -17258,7 +17258,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -17276,7 +17276,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -17291,7 +17291,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -17342,7 +17342,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -17474,7 +17474,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -17489,7 +17489,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -17522,7 +17522,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -17555,7 +17555,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -17573,7 +17573,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -17606,7 +17606,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -17672,7 +17672,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -17687,7 +17687,7 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -17720,7 +17720,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -17738,7 +17738,7 @@
         <v>6</v>
       </c>
       <c r="D33" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -17753,7 +17753,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -17786,7 +17786,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/206/inyear.xlsx
+++ b/docs/d/206/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/206/inyear.xlsx
+++ b/docs/d/206/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/206/inyear.xlsx
+++ b/docs/d/206/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/206/inyear.xlsx
+++ b/docs/d/206/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/206/inyear.xlsx
+++ b/docs/d/206/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 10 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 10 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 27 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 27 clubs short</t>
         </is>
       </c>
     </row>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>1</v>
       </c>
       <c r="U11" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V11" s="9" t="n">
         <v>1</v>
@@ -1850,7 +1850,7 @@
         <v>2</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" s="9" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -1955,8 +1955,8 @@
       <c r="S13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T13" s="9" t="n">
-        <v>0</v>
+      <c r="T13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U13" s="9" t="n">
         <v>0</v>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2543,8 +2543,8 @@
       <c r="U19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V19" s="9" t="n">
-        <v>2</v>
+      <c r="V19" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2632,10 +2632,10 @@
         <v>0</v>
       </c>
       <c r="S20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T20" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U20" s="9" t="n">
         <v>0</v>
@@ -2693,17 +2693,17 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L21" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M21" s="8" t="n">
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="P21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="9" t="n">
         <v>1</v>
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -3995,8 +3995,8 @@
       <c r="T34" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U34" s="9" t="n">
-        <v>0</v>
+      <c r="U34" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V34" s="10" t="n">
         <v>4</v>
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>0</v>
       </c>
       <c r="V41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>0</v>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5118,13 +5118,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
@@ -5162,11 +5162,11 @@
       <c r="U46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V46" s="9" t="n">
-        <v>3</v>
+      <c r="V46" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X46" s="10" t="n">
         <v>4</v>
@@ -5977,7 +5977,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -5991,13 +5991,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
@@ -6038,8 +6038,8 @@
       <c r="V55" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W55" s="9" t="n">
-        <v>3</v>
+      <c r="W55" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X55" s="10" t="n">
         <v>5</v>
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>4</v>
       </c>
       <c r="W57" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X57" s="10" t="n">
         <v>4</v>
@@ -6268,7 +6268,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6320,8 +6320,8 @@
       <c r="S58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T58" s="9" t="n">
-        <v>0</v>
+      <c r="T58" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U58" s="9" t="n">
         <v>0</v>
@@ -6573,13 +6573,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -6864,13 +6864,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>0</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
@@ -7834,13 +7834,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>52</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>4</v>
       </c>
       <c r="W74" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X74" s="10" t="n">
         <v>5</v>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -9512,8 +9512,8 @@
       <c r="P91" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q91" s="9" t="n">
-        <v>1</v>
+      <c r="Q91" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R91" s="9" t="n">
         <v>0</v>
@@ -9774,13 +9774,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -10744,13 +10744,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
@@ -10788,8 +10788,8 @@
       <c r="U104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V104" s="9" t="n">
-        <v>3</v>
+      <c r="V104" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>0</v>
       </c>
       <c r="Q121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R121" s="9" t="n">
         <v>0</v>
@@ -13211,7 +13211,7 @@
         <v>1</v>
       </c>
       <c r="U129" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V129" s="9" t="n">
         <v>2</v>
@@ -13266,13 +13266,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
@@ -13363,13 +13363,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>0</v>
       </c>
       <c r="V131" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W131" s="9" t="n">
         <v>0</v>
@@ -15594,13 +15594,13 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L154" s="7" t="inlineStr">
         <is>
@@ -15788,13 +15788,13 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L156" s="7" t="inlineStr">
         <is>
@@ -16273,13 +16273,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>0</v>
       </c>
       <c r="V161" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W161" s="9" t="n">
         <v>0</v>
@@ -16781,7 +16781,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -16814,7 +16814,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -16829,7 +16829,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -16913,7 +16913,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -17012,7 +17012,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -17078,7 +17078,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -17309,7 +17309,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -17375,7 +17375,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>

--- a/docs/d/206/inyear.xlsx
+++ b/docs/d/206/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:49 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 10 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 10 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 27 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 27 clubs short</t>
         </is>
       </c>
     </row>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>0</v>
       </c>
       <c r="V4" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W4" s="9" t="n">
         <v>0</v>
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W12" s="9" t="n">
         <v>0</v>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>-1</v>
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="P29" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q29" s="9" t="n">
         <v>0</v>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="P30" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q30" s="9" t="n">
         <v>1</v>
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -3857,13 +3857,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
@@ -3904,8 +3904,8 @@
       <c r="V33" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W33" s="9" t="n">
-        <v>3</v>
+      <c r="W33" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X33" s="10" t="n">
         <v>4</v>
@@ -5315,10 +5315,10 @@
         <v>10</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5603,13 +5603,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5647,8 +5647,8 @@
       <c r="U51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V51" s="9" t="n">
-        <v>3</v>
+      <c r="V51" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W51" s="9" t="n">
         <v>0</v>
@@ -6415,7 +6415,7 @@
         <v>0</v>
       </c>
       <c r="S59" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T59" s="9" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6573,13 +6573,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -6617,8 +6617,8 @@
       <c r="U61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V61" s="9" t="n">
-        <v>3</v>
+      <c r="V61" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>0</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
@@ -7834,13 +7834,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>52</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>4</v>
       </c>
       <c r="W74" s="10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X74" s="10" t="n">
         <v>5</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -8751,8 +8751,8 @@
       <c r="U83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V83" s="9" t="n">
-        <v>3</v>
+      <c r="V83" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
@@ -8901,17 +8901,17 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L85" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L85" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M85" s="8" t="n">
@@ -8937,16 +8937,16 @@
         <v>0</v>
       </c>
       <c r="S85" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T85" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U85" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V85" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="T85" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U85" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V85" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -9098,10 +9098,10 @@
         <v>9</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>0</v>
       </c>
       <c r="V90" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
@@ -9516,7 +9516,7 @@
         <v>2</v>
       </c>
       <c r="R91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S91" s="9" t="n">
         <v>0</v>
@@ -9898,7 +9898,7 @@
         </is>
       </c>
       <c r="P95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q95" s="9" t="n">
         <v>0</v>
@@ -10189,7 +10189,7 @@
         </is>
       </c>
       <c r="P98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q98" s="10" t="n">
         <v>2</v>
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -10744,13 +10744,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>4</v>
       </c>
       <c r="W104" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X104" s="10" t="n">
         <v>7</v>
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -10938,13 +10938,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -10976,8 +10976,8 @@
       <c r="S106" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T106" s="9" t="n">
-        <v>0</v>
+      <c r="T106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U106" s="9" t="n">
         <v>0</v>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>4</v>
       </c>
       <c r="W109" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X109" s="10" t="n">
         <v>7</v>
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11561,8 +11561,8 @@
       <c r="T112" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U112" s="9" t="n">
-        <v>0</v>
+      <c r="U112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V112" s="9" t="n">
         <v>1</v>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -11644,7 +11644,7 @@
         </is>
       </c>
       <c r="P113" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q113" s="9" t="n">
         <v>1</v>
@@ -11652,8 +11652,8 @@
       <c r="R113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S113" s="9" t="n">
-        <v>1</v>
+      <c r="S113" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T113" s="9" t="n">
         <v>0</v>
@@ -12005,13 +12005,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>0</v>
       </c>
       <c r="V117" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W117" s="9" t="n">
         <v>0</v>
@@ -12088,7 +12088,7 @@
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12102,13 +12102,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>1</v>
       </c>
       <c r="Q118" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R118" s="9" t="n">
         <v>0</v>
@@ -12143,14 +12143,14 @@
       <c r="T118" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U118" s="9" t="n">
-        <v>0</v>
+      <c r="U118" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V118" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W118" s="9" t="n">
-        <v>2</v>
+      <c r="W118" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X118" s="9" t="n">
         <v>3</v>
@@ -12379,7 +12379,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -12422,8 +12422,8 @@
       <c r="P121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q121" s="9" t="n">
-        <v>1</v>
+      <c r="Q121" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R121" s="9" t="n">
         <v>0</v>
@@ -12587,13 +12587,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-15</v>
+        <v>-3</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -12632,7 +12632,7 @@
         <v>0</v>
       </c>
       <c r="V123" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W123" s="9" t="n">
         <v>0</v>
@@ -12670,7 +12670,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -12684,13 +12684,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -12728,8 +12728,8 @@
       <c r="U124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V124" s="9" t="n">
-        <v>3</v>
+      <c r="V124" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W124" s="9" t="n">
         <v>0</v>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -12808,7 +12808,7 @@
         </is>
       </c>
       <c r="P125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q125" s="9" t="n">
         <v>0</v>
@@ -12816,8 +12816,8 @@
       <c r="R125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S125" s="9" t="n">
-        <v>1</v>
+      <c r="S125" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T125" s="9" t="n">
         <v>0</v>
@@ -14236,13 +14236,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>0</v>
       </c>
       <c r="V140" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W140" s="9" t="n">
         <v>0</v>
@@ -14333,13 +14333,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -14527,13 +14527,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -14624,13 +14624,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
@@ -14668,8 +14668,8 @@
       <c r="U144" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V144" s="9" t="n">
-        <v>3</v>
+      <c r="V144" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W144" s="9" t="n">
         <v>0</v>
@@ -14721,13 +14721,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
@@ -15109,13 +15109,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
         <v>0</v>
       </c>
       <c r="V149" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W149" s="9" t="n">
         <v>0</v>
@@ -15206,17 +15206,17 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L150" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L150" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M150" s="8" t="n">
@@ -15251,7 +15251,7 @@
         <v>0</v>
       </c>
       <c r="V150" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W150" s="9" t="n">
         <v>0</v>
@@ -15386,7 +15386,7 @@
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F152" s="6" t="n">
         <v>10</v>
@@ -15441,8 +15441,8 @@
       <c r="T152" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U152" s="9" t="n">
-        <v>0</v>
+      <c r="U152" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V152" s="9" t="n">
         <v>1</v>
@@ -15788,13 +15788,13 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L156" s="7" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>0</v>
       </c>
       <c r="Q163" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R163" s="9" t="n">
         <v>0</v>
@@ -16913,7 +16913,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -17111,7 +17111,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -17243,7 +17243,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -17291,7 +17291,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -17408,7 +17408,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -17441,7 +17441,7 @@
         <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -17474,13 +17474,13 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -17507,7 +17507,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -17672,7 +17672,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -17705,7 +17705,7 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -17720,7 +17720,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
